--- a/submissions/07-freight-invoice-audit/inputs/northline_contract_rates_2026.xlsx
+++ b/submissions/07-freight-invoice-audit/inputs/northline_contract_rates_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8022D698-4F26-E640-9FF8-FE380AA4B5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4EB76C-4FA5-F646-A2D2-9542A91447A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/submissions/07-freight-invoice-audit/inputs/northline_contract_rates_2026.xlsx
+++ b/submissions/07-freight-invoice-audit/inputs/northline_contract_rates_2026.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4EB76C-4FA5-F646-A2D2-9542A91447A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74810FE-36BF-3B4F-8C75-A24363C3DEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lane Rates" sheetId="1" r:id="rId1"/>

--- a/submissions/07-freight-invoice-audit/inputs/northline_contract_rates_2026.xlsx
+++ b/submissions/07-freight-invoice-audit/inputs/northline_contract_rates_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74810FE-36BF-3B4F-8C75-A24363C3DEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FDE0FF-B2E5-1848-8DB4-B6F65F480E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
